--- a/文法（ぶんぽう）/汉语语法.xlsx
+++ b/文法（ぶんぽう）/汉语语法.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\文法（ぶんぽう）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C870FB-4A3D-424E-9002-C560AE5D2E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3D05EC-F1DE-4F1B-A431-46FF4B3A6F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="恋人「こい」" sheetId="4" state="hidden" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="2041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="2040">
   <si>
     <t>…は…です</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -12013,10 +12013,6 @@
       </rPr>
       <t>+强调结果</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>心情变沉重了</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -19847,36 +19843,36 @@
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1657</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="9" t="s">
         <v>1659</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>1282</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>1284</v>
-      </c>
       <c r="E3" s="9" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -19884,21 +19880,21 @@
         <v>1066</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="9" t="s">
         <v>1208</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1308</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1309</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="9"/>
@@ -19906,80 +19902,80 @@
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>1715</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>310</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>1402</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1401</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>1404</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>1432</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1431</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -19990,18 +19986,18 @@
         <v>302</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>1406</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1195</v>
@@ -20015,282 +20011,282 @@
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E14" t="s">
         <v>1356</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E15" t="s">
         <v>1352</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E16" t="s">
         <v>1354</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>1503</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>1537</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D18" t="s">
         <v>1538</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1539</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>1506</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B20" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B22" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>2011</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>2012</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" t="s">
         <v>2013</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2014</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>972</v>
       </c>
       <c r="D23" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E23" t="s">
         <v>1346</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>1650</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B25" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="9"/>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E27" t="s">
         <v>1653</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B28" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>1939</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>1940</v>
-      </c>
       <c r="D28" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E28" t="s">
         <v>1661</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="51"/>
       <c r="B30" s="52" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E30" s="37" t="s">
         <v>1213</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B31" s="52" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E31" s="37" t="s">
         <v>1731</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E32" s="37"/>
     </row>
     <row r="33" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E33" s="37" t="s">
         <v>1728</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C34" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D34" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>1310</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>1807</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" t="s">
         <v>1809</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" s="37" t="s">
         <v>1810</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>1811</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="37" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -20326,19 +20322,19 @@
     </row>
     <row r="38" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>1021</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D38" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E38" t="s">
         <v>1216</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -20346,143 +20342,143 @@
         <v>1021</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D39" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E39" s="37" t="s">
         <v>1264</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" t="s">
         <v>1522</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>1523</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="D42" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E42" t="s">
         <v>1629</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>1622</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>1623</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>1621</v>
-      </c>
       <c r="D44" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E44" t="s">
         <v>1627</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C45" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D45" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="E45" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>1893</v>
-      </c>
       <c r="D46" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E46" t="s">
         <v>1897</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D47" t="s">
         <v>1894</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>1895</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1896</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E48" t="s">
         <v>1900</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1899</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1901</v>
       </c>
     </row>
   </sheetData>
@@ -20503,73 +20499,73 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1737</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1739</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>1845</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D7" t="s">
         <v>1977</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>310</v>
@@ -20577,55 +20573,55 @@
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D9" t="s">
         <v>2009</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2010</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>1744</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>1745</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C11" t="s">
         <v>1817</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>1818</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="B12" s="1" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C12" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D12" t="s">
         <v>1820</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1821</v>
       </c>
     </row>
   </sheetData>
@@ -20852,19 +20848,19 @@
     </row>
     <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>1673</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="C16" s="1" t="s">
         <v>1674</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" t="s">
         <v>1676</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -20944,74 +20940,74 @@
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B23" t="s">
         <v>1334</v>
       </c>
-      <c r="B23" t="s">
-        <v>1335</v>
-      </c>
       <c r="C23" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E23" t="s">
         <v>1337</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D24" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E24" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C25" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E25" t="s">
         <v>1438</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E26" t="s">
         <v>1440</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C27" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E27" t="s">
         <v>1442</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C28" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E28" t="s">
         <v>1445</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -21033,52 +21029,52 @@
     </row>
     <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="9" t="s">
         <v>1314</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E31" t="s">
         <v>1317</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>1568</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>1569</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>1571</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="33" spans="4:5" ht="18" x14ac:dyDescent="0.45">
       <c r="D33" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E33" t="s">
         <v>1573</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1574</v>
       </c>
     </row>
   </sheetData>
@@ -21187,19 +21183,19 @@
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E8" t="s">
         <v>1945</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1948</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -21207,65 +21203,65 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="E9" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="25" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D10" t="s">
         <v>2037</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>2038</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>1566</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>1592</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="D13" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E13" t="s">
         <v>1593</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -21273,55 +21269,55 @@
         <v>328</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E14" t="s">
         <v>1599</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C15" s="1" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D15" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E15" t="s">
         <v>1601</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>1934</v>
       </c>
-      <c r="B16" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1935</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E16" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E17" t="s">
         <v>1937</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1936</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -21329,132 +21325,132 @@
         <v>1067</v>
       </c>
       <c r="B18" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D18" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E18" t="s">
         <v>1697</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D19" t="s">
         <v>1970</v>
       </c>
-      <c r="B19" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1969</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>1971</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B20" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E20" t="s">
         <v>1699</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="D21" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E21" s="54" t="s">
         <v>1931</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>2004</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2005</v>
       </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>1747</v>
       </c>
-      <c r="B23" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1748</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E23" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E24" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E25" t="s">
         <v>1753</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B26" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
   </sheetData>
@@ -21706,41 +21702,41 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="13"/>
       <c r="B15" s="40" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E15" t="s">
         <v>1588</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="13"/>
       <c r="B16" s="40"/>
       <c r="D16" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E16" t="s">
         <v>1586</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="13"/>
       <c r="B17" s="40" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E17" t="s">
         <v>1929</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1928</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -21751,7 +21747,7 @@
         <v>50</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>134</v>
@@ -21779,52 +21775,52 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>1452</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
       <c r="B21" s="10"/>
       <c r="C21" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="9" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>1450</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D23" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>1454</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -21832,80 +21828,80 @@
         <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>1989</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="9" t="s">
         <v>1990</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="9" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>1560</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="9" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="9" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
@@ -21948,7 +21944,7 @@
         <v>388</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>663</v>
@@ -21965,7 +21961,7 @@
         <v>666</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>663</v>
@@ -21990,36 +21986,36 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="24" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>328</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>1609</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" t="s">
         <v>1610</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="24" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>328</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>1635</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="9" t="s">
         <v>1636</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -22027,7 +22023,7 @@
         <v>954</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>951</v>
@@ -22043,19 +22039,19 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D9" t="s">
         <v>1681</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1" t="s">
         <v>1682</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>1683</v>
       </c>
     </row>
   </sheetData>
@@ -22676,7 +22672,7 @@
         <v>508</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D3" t="s">
         <v>509</v>
@@ -22695,13 +22691,13 @@
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C5" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D5" t="s">
         <v>1814</v>
       </c>
-      <c r="D5" t="s">
-        <v>1815</v>
-      </c>
       <c r="E5" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -22709,76 +22705,76 @@
         <v>507</v>
       </c>
       <c r="B6" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="E6" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="13"/>
       <c r="C7" s="55"/>
       <c r="D7" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E7" t="s">
         <v>1980</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1981</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E8" t="s">
         <v>1582</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1583</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C9" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E9" t="s">
         <v>1723</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C10" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="E10" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B11" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>1982</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>1983</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>1984</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1985</v>
       </c>
     </row>
   </sheetData>
@@ -23002,52 +22998,52 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="9" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B12" s="47" t="s">
         <v>328</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="9" t="s">
         <v>1414</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="9"/>
       <c r="B13" s="47"/>
       <c r="D13" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>1416</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="47"/>
       <c r="D14" s="23" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="47"/>
       <c r="C15" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D15" t="s">
         <v>1410</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>1411</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1412</v>
       </c>
     </row>
   </sheetData>
@@ -23105,7 +23101,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>374</v>
@@ -23201,70 +23197,70 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="D9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E9" t="s">
         <v>1866</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="D10" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E10" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="15" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="D11" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="E11" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="15" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>1855</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>1856</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="9" t="s">
         <v>1857</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -23387,7 +23383,7 @@
         <v>967</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>800</v>
@@ -23402,7 +23398,7 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="17"/>
       <c r="B22" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>801</v>
@@ -23417,7 +23413,7 @@
         <v>968</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>918</v>
@@ -23432,7 +23428,7 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="17"/>
       <c r="B24" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>919</v>
@@ -23464,7 +23460,7 @@
         <v>898</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>920</v>
@@ -23476,7 +23472,7 @@
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>921</v>
@@ -23491,7 +23487,7 @@
         <v>822</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>922</v>
@@ -23508,7 +23504,7 @@
         <v>823</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>923</v>
@@ -23523,7 +23519,7 @@
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>924</v>
@@ -23555,7 +23551,7 @@
         <v>56</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>925</v>
@@ -23567,7 +23563,7 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="15"/>
       <c r="B33" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>926</v>
@@ -23596,7 +23592,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="15"/>
       <c r="B35" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>927</v>
@@ -23608,7 +23604,7 @@
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="15"/>
       <c r="B36" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>928</v>
@@ -23619,110 +23615,110 @@
     </row>
     <row r="37" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="18" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>1679</v>
-      </c>
       <c r="D37" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>1676</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="18"/>
       <c r="B38" s="6"/>
       <c r="D38" s="54" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E38" t="s">
         <v>1876</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="18" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D39" t="s">
         <v>1873</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>1874</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="18" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" t="s">
         <v>1879</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" s="9" t="s">
         <v>1880</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="18" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="9" t="s">
         <v>1704</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="18" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>1882</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>1883</v>
-      </c>
       <c r="D42" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E42" t="s">
         <v>1887</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="18"/>
       <c r="B43" s="6"/>
       <c r="C43" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D43" t="s">
         <v>1884</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>1885</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
@@ -23943,50 +23939,50 @@
     </row>
     <row r="59" spans="1:5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>1544</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="60" spans="1:5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="9" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D61" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="E61" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -23994,13 +23990,13 @@
         <v>328</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="E62" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -24008,78 +24004,78 @@
         <v>328</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E63" t="s">
         <v>1554</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1555</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="9" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E64" t="s">
         <v>1588</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B65" s="40"/>
       <c r="D65" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E65" t="s">
         <v>1586</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B66" s="56" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>1994</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>1995</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>1996</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="67" spans="1:5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>1605</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="68" spans="1:5" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="D68" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E68" t="s">
         <v>1607</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1608</v>
       </c>
     </row>
   </sheetData>
@@ -24868,125 +24864,125 @@
     </row>
     <row r="47" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" s="15" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>1327</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A48" s="15" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>1332</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B49" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E49" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F49" t="s">
         <v>2030</v>
-      </c>
-      <c r="F49" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B50" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>2018</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2019</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A51" s="15"/>
       <c r="B51" s="1" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B52" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B53" s="1" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B54" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B55" s="1" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F55" t="s">
         <v>1923</v>
-      </c>
-      <c r="F55" t="s">
-        <v>1924</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -25019,22 +25015,22 @@
     </row>
     <row r="58" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A58" s="18" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>328</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E58" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F58" t="s">
         <v>1376</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -25042,10 +25038,10 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F59" t="s">
         <v>1374</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -25054,10 +25050,10 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F60" t="s">
         <v>1378</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -25160,36 +25156,36 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>1640</v>
       </c>
-      <c r="D6" s="25" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="9" t="s">
         <v>1641</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>1647</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>1648</v>
       </c>
     </row>
   </sheetData>
@@ -25223,10 +25219,10 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E1" s="60" t="s">
         <v>1115</v>
@@ -25237,7 +25233,7 @@
       </c>
       <c r="J1" s="11"/>
       <c r="K1" s="10" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="L1" s="36" t="s">
         <v>1141</v>
@@ -25246,13 +25242,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1105</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>1102</v>
@@ -25261,10 +25257,10 @@
         <v>1106</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2" s="41" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="I2" s="37" t="s">
         <v>1109</v>
@@ -25273,7 +25269,7 @@
         <v>1111</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -25292,7 +25288,7 @@
       </c>
       <c r="G3" s="60"/>
       <c r="H3" s="36" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>1113</v>
@@ -25302,16 +25298,16 @@
       </c>
       <c r="K3" s="60"/>
       <c r="L3" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>1232</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>1233</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>1235</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -25333,7 +25329,7 @@
       </c>
       <c r="G4" s="60"/>
       <c r="H4" s="36" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>1114</v>
@@ -25345,7 +25341,7 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="E6" s="60" t="s">
         <v>1124</v>
@@ -25369,7 +25365,7 @@
         <v>1120</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>1125</v>
@@ -25378,10 +25374,10 @@
         <v>1128</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>1129</v>
@@ -25390,7 +25386,7 @@
         <v>1131</v>
       </c>
       <c r="K7" s="59" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>1144</v>
@@ -25424,7 +25420,7 @@
       </c>
       <c r="G8" s="61"/>
       <c r="H8" s="10" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>1130</v>
@@ -25448,7 +25444,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D10" s="11" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="E10" s="60" t="s">
         <v>1116</v>
@@ -25472,28 +25468,28 @@
         <v>1133</v>
       </c>
       <c r="D11" s="59" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>1140</v>
       </c>
       <c r="G11" s="59" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>1137</v>
       </c>
       <c r="K11" s="59" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>1151</v>
@@ -25520,17 +25516,17 @@
       </c>
       <c r="D12" s="61"/>
       <c r="E12" s="6" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>1139</v>
       </c>
       <c r="G12" s="61"/>
       <c r="H12" s="10" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>1138</v>
@@ -25539,10 +25535,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C14" s="6" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
   </sheetData>
@@ -27587,7 +27583,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="15" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>724</v>
@@ -27604,7 +27600,7 @@
     </row>
     <row r="15" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="15" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>649</v>
@@ -27717,7 +27713,7 @@
         <v>815</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27731,10 +27727,7 @@
         <v>588</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>602</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27750,9 +27743,6 @@
       <c r="D4" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>603</v>
-      </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
@@ -27765,7 +27755,7 @@
         <v>392</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27779,7 +27769,7 @@
         <v>393</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27795,7 +27785,9 @@
       <c r="D7" t="s">
         <v>366</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="9" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
@@ -27808,7 +27800,7 @@
         <v>364</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>445</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27821,28 +27813,30 @@
       <c r="D9" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="45" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>457</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>233</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>50</v>
@@ -27854,12 +27848,12 @@
         <v>937</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="46" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>50</v>
@@ -27869,9 +27863,6 @@
       </c>
       <c r="D12" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27882,7 +27873,7 @@
         <v>660</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>1200</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -27901,19 +27892,19 @@
     </row>
     <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>1466</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1465</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -27948,79 +27939,79 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1690</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="9" t="s">
         <v>1691</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="9"/>
       <c r="C3" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="D3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E3" t="s">
         <v>1853</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="15"/>
       <c r="C4" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="9"/>
       <c r="C5" s="1" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="D5" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E5" t="s">
         <v>1849</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="9"/>
       <c r="C6" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D6" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E6" t="s">
         <v>1851</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="9"/>
       <c r="C7" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D7" t="s">
         <v>1925</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>1926</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -28029,30 +28020,30 @@
         <v>328</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D8" t="s">
         <v>2006</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="9" t="s">
         <v>2007</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>2008</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>1381</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -28132,44 +28123,44 @@
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D15" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E15" t="s">
         <v>1514</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="C16" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D17" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="E17" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -28177,7 +28168,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -28188,49 +28179,49 @@
         <v>328</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D19" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E19" t="s">
         <v>1769</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="C21" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="9" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>1665</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" t="s">
         <v>1666</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>1667</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1668</v>
       </c>
     </row>
   </sheetData>
@@ -28262,162 +28253,162 @@
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1292</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="9"/>
       <c r="B4" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1298</v>
-      </c>
       <c r="D5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>1303</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="9" t="s">
         <v>1299</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="9" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>2023</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2022</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="9" t="s">
         <v>2024</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="9" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D8" t="s">
         <v>1534</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1533</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>1535</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D10" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B11" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B12" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -28428,7 +28419,7 @@
         <v>724</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D14" s="31" t="s">
         <v>756</v>
@@ -28452,141 +28443,141 @@
       <c r="A16" s="1"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>1254</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>1470</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1485</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C18" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E18" t="s">
         <v>1474</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C19" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D19" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E19" t="s">
         <v>1476</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B20" t="s">
         <v>1484</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" t="s">
         <v>1486</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1487</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>1772</v>
       </c>
-      <c r="B21" t="s">
-        <v>1485</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>1773</v>
-      </c>
       <c r="D21" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E21" t="s">
         <v>1775</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>1777</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" t="s">
         <v>1778</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C23" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B24" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="D25" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E25" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="B26" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="D26" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E26" t="s">
         <v>1827</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1828</v>
       </c>
     </row>
   </sheetData>
@@ -28628,37 +28619,37 @@
         <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="9"/>
       <c r="C3" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>1390</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="9"/>
       <c r="C4" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1833</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="9" t="s">
         <v>1834</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -28672,15 +28663,15 @@
         <v>991</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>1275</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>992</v>
@@ -28689,7 +28680,7 @@
         <v>999</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -28697,10 +28688,10 @@
         <v>993</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -28712,24 +28703,24 @@
         <v>1001</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="9" t="s">
         <v>1365</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -28737,15 +28728,15 @@
         <v>328</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C11" s="1" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
   </sheetData>
@@ -28799,10 +28790,10 @@
         <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="E3" t="s">
         <v>728</v>
@@ -28813,76 +28804,76 @@
         <v>328</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1964</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>1965</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>1966</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="18" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1784</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>1785</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="9" t="s">
         <v>1786</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" s="18"/>
       <c r="C6" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D6" t="s">
         <v>1788</v>
       </c>
-      <c r="D6" t="s">
-        <v>1789</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>2026</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>2027</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="9" t="s">
         <v>2028</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>1941</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
         <v>1942</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>1943</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.2" x14ac:dyDescent="0.35">
@@ -28929,101 +28920,101 @@
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>1396</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="C14" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>1362</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>1791</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>1800</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B19" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B20" s="1" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -29036,10 +29027,10 @@
         <v>518</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1398</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1399</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>545</v>
@@ -29047,61 +29038,61 @@
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="37" t="s">
         <v>1273</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C23" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" t="s">
         <v>1577</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>1605</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E25" t="s">
         <v>1607</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1608</v>
       </c>
     </row>
   </sheetData>
@@ -29141,29 +29132,29 @@
     </row>
     <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="49" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>1384</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B3" s="9"/>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -29172,82 +29163,82 @@
         <v>186</v>
       </c>
       <c r="D4" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E4" t="s">
         <v>1992</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1993</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E5" t="s">
         <v>1998</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1999</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" s="9"/>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E6" t="s">
         <v>2015</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2016</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" t="s">
         <v>1320</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="9" t="s">
         <v>1321</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E8" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D9" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E9" t="s">
         <v>1757</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B10" s="9" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>1613</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E10" t="s">
         <v>1614</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1616</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
@@ -29256,69 +29247,69 @@
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="23" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E12" t="s">
         <v>1530</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1529</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="23"/>
       <c r="B13" s="9"/>
       <c r="C13" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D13" t="s">
         <v>1526</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1527</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="23"/>
       <c r="B14" s="9" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>1911</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" t="s">
         <v>1912</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>1913</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="23"/>
       <c r="B15" s="9" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C15" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="D15" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E15" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="23"/>
       <c r="B16" s="9"/>
       <c r="C16" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -29326,252 +29317,252 @@
       <c r="A17" s="23"/>
       <c r="B17" s="53"/>
       <c r="C17" s="1" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="D17" t="s">
+        <v>1908</v>
+      </c>
+      <c r="E17" t="s">
         <v>1909</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="23"/>
       <c r="B18" s="9" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>1918</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E18" t="s">
         <v>1919</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2017</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="C19" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>2001</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" t="s">
         <v>2002</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="23"/>
       <c r="B20" s="9" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C20" t="s">
         <v>1903</v>
       </c>
-      <c r="C20" t="s">
-        <v>1904</v>
-      </c>
       <c r="D20" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E20" t="s">
         <v>1687</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="23"/>
       <c r="B21" s="9"/>
       <c r="C21" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="23"/>
       <c r="B22" s="9"/>
       <c r="C22" s="1" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B23" s="9" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B24" s="9"/>
       <c r="C24" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D24" t="s">
         <v>1481</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>1482</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B25" s="9"/>
       <c r="C25" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B26" s="9" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D26" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E26" t="s">
         <v>1757</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B27" s="9"/>
       <c r="C27" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D27" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E27" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B28" s="9"/>
       <c r="C28" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D28" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E28" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B29" s="9"/>
       <c r="C29" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="D29" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E29" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B30" s="9" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>1670</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E30" t="s">
         <v>1671</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B31" s="9" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C31" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E31" t="s">
         <v>1202</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C32" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D32" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E32" t="s">
         <v>1204</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B33" s="9" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="D33" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E33" t="s">
         <v>1422</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B34" s="9" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="D34" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E34" t="s">
         <v>1420</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>1954</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>1955</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B36" s="9" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C36" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E36" t="s">
         <v>1267</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B37" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -29584,10 +29575,10 @@
         <v>870</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>1424</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>1425</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -29600,7 +29591,7 @@
         <v>869</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>873</v>
@@ -29610,62 +29601,62 @@
     </row>
     <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B40" s="9" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>1427</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>1428</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B41" s="9" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>2032</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>2033</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="9" t="s">
         <v>2034</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>2035</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D42" t="s">
         <v>1486</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>1487</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>1973</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>1976</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>1974</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.45">
@@ -29673,19 +29664,19 @@
     </row>
     <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A45" s="49" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1261</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>1021</v>
       </c>
       <c r="D45" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E45" t="s">
         <v>1257</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.45">
@@ -29742,66 +29733,66 @@
     </row>
     <row r="50" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>1460</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1464</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D51" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>1462</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>1489</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" t="s">
         <v>1490</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" s="9" t="s">
         <v>1491</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B53" s="9" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D53" t="s">
         <v>1494</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" s="9" t="s">
         <v>1495</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>1497</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>1498</v>
       </c>
     </row>
   </sheetData>

--- a/文法（ぶんぽう）/汉语语法.xlsx
+++ b/文法（ぶんぽう）/汉语语法.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\文法（ぶんぽう）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3D05EC-F1DE-4F1B-A431-46FF4B3A6F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508D0C0A-0530-4BDA-8F6B-811B9546F067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" firstSheet="15" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="恋人「こい」" sheetId="4" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="仮定「かてい」" sheetId="15" r:id="rId8"/>
     <sheet name="時間&amp;空間" sheetId="25" r:id="rId9"/>
     <sheet name="範囲「はんい」" sheetId="22" r:id="rId10"/>
-    <sheet name="問題" sheetId="27" r:id="rId11"/>
+    <sheet name="問題「もんだい」" sheetId="27" r:id="rId11"/>
     <sheet name="目的「もくてき」" sheetId="5" r:id="rId12"/>
     <sheet name="认为" sheetId="20" r:id="rId13"/>
     <sheet name="要請「ようせい」、招待「しょうたい」" sheetId="3" r:id="rId14"/>
@@ -19494,19 +19494,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -25224,10 +25224,10 @@
       <c r="D1" s="11" t="s">
         <v>1950</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="61" t="s">
         <v>1115</v>
       </c>
-      <c r="F1" s="60"/>
+      <c r="F1" s="61"/>
       <c r="I1" s="36" t="s">
         <v>1117</v>
       </c>
@@ -25279,14 +25279,14 @@
       <c r="C3" s="43" t="s">
         <v>1097</v>
       </c>
-      <c r="D3" s="60"/>
+      <c r="D3" s="61"/>
       <c r="E3" s="6" t="s">
         <v>1103</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="G3" s="60"/>
+      <c r="G3" s="61"/>
       <c r="H3" s="36" t="s">
         <v>1220</v>
       </c>
@@ -25296,7 +25296,7 @@
       <c r="J3" s="11" t="s">
         <v>1110</v>
       </c>
-      <c r="K3" s="60"/>
+      <c r="K3" s="61"/>
       <c r="L3" s="6" t="s">
         <v>1231</v>
       </c>
@@ -25320,14 +25320,14 @@
       <c r="C4" s="6" t="s">
         <v>1098</v>
       </c>
-      <c r="D4" s="60"/>
+      <c r="D4" s="61"/>
       <c r="E4" s="6" t="s">
         <v>1104</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="G4" s="60"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="36" t="s">
         <v>1221</v>
       </c>
@@ -25337,16 +25337,16 @@
       <c r="J4" s="6" t="s">
         <v>1112</v>
       </c>
-      <c r="K4" s="60"/>
+      <c r="K4" s="61"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
         <v>1951</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="61" t="s">
         <v>1124</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="61"/>
       <c r="I6" s="36" t="s">
         <v>1118</v>
       </c>
@@ -25411,14 +25411,14 @@
       <c r="C8" s="6" t="s">
         <v>1121</v>
       </c>
-      <c r="D8" s="61"/>
+      <c r="D8" s="60"/>
       <c r="E8" s="6" t="s">
         <v>1126</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>1127</v>
       </c>
-      <c r="G8" s="61"/>
+      <c r="G8" s="60"/>
       <c r="H8" s="10" t="s">
         <v>1223</v>
       </c>
@@ -25428,7 +25428,7 @@
       <c r="J8" s="11" t="s">
         <v>1132</v>
       </c>
-      <c r="K8" s="61"/>
+      <c r="K8" s="60"/>
       <c r="L8" s="6" t="s">
         <v>1147</v>
       </c>
@@ -25446,10 +25446,10 @@
       <c r="D10" s="11" t="s">
         <v>1952</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="61" t="s">
         <v>1116</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="61"/>
       <c r="I10" s="36" t="s">
         <v>1119</v>
       </c>
@@ -25514,14 +25514,14 @@
       <c r="C12" s="6" t="s">
         <v>1135</v>
       </c>
-      <c r="D12" s="61"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="6" t="s">
         <v>1226</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>1139</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="60"/>
       <c r="H12" s="10" t="s">
         <v>1225</v>
       </c>
@@ -25531,7 +25531,7 @@
       <c r="J12" s="11" t="s">
         <v>1138</v>
       </c>
-      <c r="K12" s="61"/>
+      <c r="K12" s="60"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C14" s="6" t="s">
@@ -25543,11 +25543,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D2:D4"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="K11:K12"/>
@@ -25555,6 +25550,11 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="G2:G4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D2:D4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25613,8 +25613,8 @@
       <c r="D2" s="62" t="s">
         <v>1167</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="38" t="s">
         <v>1170</v>
       </c>
@@ -25644,10 +25644,10 @@
       <c r="A5" s="10" t="s">
         <v>1163</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
       <c r="F5" s="64"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -28418,7 +28418,7 @@
       <c r="B14" s="15" t="s">
         <v>724</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="58" t="s">
         <v>1255</v>
       </c>
       <c r="D14" s="31" t="s">
@@ -28431,7 +28431,7 @@
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="31"/>
       <c r="B15" s="15"/>
-      <c r="C15" s="57"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="31" t="s">
         <v>941</v>
       </c>
@@ -28897,7 +28897,7 @@
       <c r="B10" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>761</v>
       </c>
       <c r="D10" s="31" t="s">
@@ -28906,14 +28906,14 @@
     </row>
     <row r="11" spans="1:5" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A11" s="31"/>
-      <c r="C11" s="58"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="31" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32.4" x14ac:dyDescent="0.25">
       <c r="A12" s="31"/>
-      <c r="C12" s="58"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="31" t="s">
         <v>944</v>
       </c>
